--- a/bench/data/files/synthetic7_A.xlsx
+++ b/bench/data/files/synthetic7_A.xlsx
@@ -549,17 +549,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Drift Foods</t>
+          <t>Xenith AG</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -569,35 +569,35 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2011-03-10</t>
+          <t>2010-07-28</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2016-02-19</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>852.9</v>
+        <v>84</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2642.2</v>
+        <v>64.2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>116.1</v>
+        <v>12.6</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>157.7</v>
+        <v>24.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>354.5</v>
+        <v>28.2</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.719</v>
+        <v>0.703</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Ravi Lopez; Mark Mueller; Elena Fischer; Emma Yamamoto</t>
+          <t>Daniel Johnson; Elena Zhang; Mark Evans</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -609,17 +609,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Glacier Logic</t>
+          <t>Nova AG</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -629,35 +629,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2013-10-18</t>
+          <t>2011-04-21</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2018-08-20</t>
+          <t>2015-05-19</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1270.4</v>
+        <v>1305.4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2052.5</v>
+        <v>1627.6</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>112.5</v>
+        <v>213.9</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>133.3</v>
+        <v>209.7</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>76.7</v>
+        <v>546.8</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.957</v>
+        <v>0.851</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Emma Gupta; Michael O'Brien</t>
+          <t>James Qureshi; Hannah Gupta; Michael O'Brien</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -669,17 +669,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Apex Networks</t>
+          <t>Iris Logistics</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -689,35 +689,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010-04-28</t>
+          <t>2011-10-27</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2017-01-17</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>59.1</v>
+        <v>1341</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>202.2</v>
+        <v>2669.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>313.8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>496.7</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>26.9</v>
+        <v>643.9</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.96</v>
+        <v>0.846</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Olivia Rossi; Robert Ueno</t>
+          <t>Ravi Zhang; Wei Hassan; Ahmed Vega; Sarah Mueller; Thomas Ivanov</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -729,17 +729,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Echo GmbH</t>
+          <t>Iris Labs</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -749,35 +749,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2013-02-05</t>
+          <t>2011-12-22</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2020-04-04</t>
+          <t>2016-02-24</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>472.9</v>
+        <v>232.1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>902.7</v>
+        <v>267.9</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>121.4</v>
+        <v>117.9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>240.5</v>
+        <v>27.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.423</v>
+        <v>0.308</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Yuki Davis; Michael Lopez</t>
+          <t>Matthew Gupta; Christopher Johnson; Michael Davis</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Drift Industries</t>
+          <t>Wavelength Energy</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -809,35 +809,35 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2012-11-15</t>
+          <t>2012-02-20</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2016-12-12</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1061</v>
+        <v>341.4</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1878.9</v>
+        <v>820.7</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>90.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>178.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>204.2</v>
+        <v>396.7</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.176</v>
+        <v>0.853</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Daniel Hassan; Matthew Qureshi; Jessica Anderson; Christopher Mueller</t>
+          <t>Olivia Xu; Hannah Evans</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -849,17 +849,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ember Solutions</t>
+          <t>Halo Networks</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -869,35 +869,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2011-11-25</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1519.9</v>
+        <v>812.1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5296.3</v>
+        <v>1219.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>353.1</v>
+        <v>189.4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>854.3</v>
+        <v>330.6</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>282.8</v>
+        <v>691</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.739</v>
+        <v>0.926</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Mark Fischer; Wei Mueller; Jennifer Xu; Thomas Nakamura; Olivia Schmidt</t>
+          <t>Ravi Patel; Yuki Davis; Ahmed Johnson; Matthew Yamamoto</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -909,51 +909,55 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Echo Networks</t>
+          <t>Halo Solutions</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2011-09-11</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>2013-03-03</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2017-03-10</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
-        <v>375.4</v>
+        <v>762.6</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v/>
+        <v>1032.1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>44.9</v>
+        <v>188.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v/>
+        <v>340.3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>177.5</v>
+        <v>782.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.152</v>
+        <v>0.41</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Hannah Xu; David Nakamura</t>
+          <t>Sarah Davis; James Vega</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -965,17 +969,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Inc</t>
+          <t>Zenith Group</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -985,35 +989,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2012-01-19</t>
+          <t>2013-02-12</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2019-12-13</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1480.1</v>
+        <v>952.8</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3920.1</v>
+        <v>1507.6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>150.9</v>
+        <v>212.9</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>165.7</v>
+        <v>361.3</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>434.6</v>
+        <v>230.6</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.204</v>
+        <v>0.895</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>David Qureshi; Wei Xu</t>
+          <t>Robert Fischer; Ahmed Ivanov</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1025,77 +1029,73 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Group</t>
+          <t>Quanta Media</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2012-05-09</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>2016-03-12</t>
-        </is>
-      </c>
+          <t>2013-02-14</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
-        <v>928.1</v>
+        <v>1624.8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2348.1</v>
+        <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>213</v>
+        <v>222.7</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>423.6</v>
+        <v/>
       </c>
       <c r="K13" s="4" t="n">
-        <v>572</v>
+        <v>763.3</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.296</v>
+        <v>0.279</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Rachel Xu; Jennifer Ueno</t>
+          <t>Robert Patel; Andrew Fischer; Ravi Kim; Jessica Yamamoto; Michael Anderson</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund I</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Inc</t>
+          <t>Cobalt Corp</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1105,57 +1105,57 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>261.2</v>
+        <v>1949.5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>313.4</v>
+        <v>3498.6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>287.5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>73</v>
+        <v>521.3</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>146.8</v>
+        <v>187.4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.171</v>
+        <v>0.245</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Ravi Johnson; Sarah Johnson; Michael Nakamura</t>
+          <t>David Lopez; Amanda Vega</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund I</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Indigo Media</t>
+          <t>Meridian Industries</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1165,57 +1165,57 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2013-09-16</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1626.1</v>
+        <v>1594.8</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2436.8</v>
+        <v>4105.9</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>297.1</v>
+        <v>306.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>376</v>
+        <v>325.7</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>785.9</v>
+        <v>467</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.921</v>
+        <v>0.473</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Robert Chen; Andrew Qureshi; Christopher Ueno</t>
+          <t>Jessica Hassan; Sarah Fischer; Ravi Johnson</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund I</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Umbra SA</t>
+          <t>Mosaic Partners</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1225,57 +1225,57 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2015-10-22</t>
+          <t>2010-04-25</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2015-06-27</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>528.5</v>
+        <v>423.5</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1022.9</v>
+        <v>1034</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>81.2</v>
+        <v>55</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>152.6</v>
+        <v>108.3</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>150.7</v>
+        <v>163.2</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.267</v>
+        <v>0.238</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Elena Anderson; Mark Xu; Rachel Yamamoto</t>
+          <t>Hannah Hassan; Hannah Vega</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund I</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Meridian Bio</t>
+          <t>Junction Logic</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1285,35 +1285,35 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2012-09-28</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2016-10-27</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>967.7</v>
+        <v>759.7</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2776.4</v>
+        <v>856.1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>263.9</v>
+        <v>106.6</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>564.2</v>
+        <v>112</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>469</v>
+        <v>248.7</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.985</v>
+        <v>0.338</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Daniel Yamamoto; Rachel O'Brien</t>
+          <t>Michael Xu; Mark Zhang; Ravi Evans; Michael Lopez</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1325,17 +1325,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Radial Foods</t>
+          <t>Bloom Industries</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1345,35 +1345,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
+          <t>2014-09-12</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1205.4</v>
+        <v>406.8</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3336.4</v>
+        <v>312</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>218.6</v>
+        <v>48.2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>227</v>
+        <v>76.8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>982.5</v>
+        <v>62.8</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.776</v>
+        <v>0.381</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Andrew Rossi; Wei Brown; Yuki Johnson; Priya Anderson; Emma Ueno</t>
+          <t>Yuki Davis; Andrew Hassan; James Qureshi; Olivia Patel; Olivia Fischer</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Atlas Foods</t>
+          <t>Atlas Materials</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1405,35 +1405,35 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2013-07-21</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
+          <t>2020-09-19</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>481.5</v>
+        <v>1136.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1414.2</v>
+        <v>3916.6</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>96.3</v>
+        <v>250.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>165.5</v>
+        <v>468</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>286.2</v>
+        <v>645.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.901</v>
+        <v>0.844</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Jessica Nakamura; Sophie O'Brien; Rachel Johnson; Sophie Chen</t>
+          <t>Mark Qureshi; Jennifer Davis; Laura Vega; Robert Nakamura</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1445,17 +1445,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Iris GmbH</t>
+          <t>Bloom Group</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2015-01-22</t>
+          <t>2013-01-13</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2018-12-29</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>454.2</v>
+        <v>1809.4</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1265.1</v>
+        <v>1482.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>43.4</v>
+        <v>158.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>78.2</v>
+        <v>327.2</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>170.6</v>
+        <v>348.8</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.989</v>
+        <v>0.756</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Wei Williams; Sophie Johnson; Sarah Xu; James Ueno; Amanda Davis</t>
+          <t>Jennifer Fischer; Emma Qureshi; Christopher Patel; Daniel Yamamoto</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1505,17 +1505,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Echo Holdings</t>
+          <t>Forge SA</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1525,35 +1525,35 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2015-05-28</t>
+          <t>2015-03-13</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2019-04-10</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>506.3</v>
+        <v>653.6</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1523.4</v>
+        <v>1620.4</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>48.4</v>
+        <v>135</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>71</v>
+        <v>302.9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>42</v>
+        <v>225.2</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.509</v>
+        <v>0.885</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Jennifer Hassan; Hannah Ivanov; Amanda Gupta</t>
+          <t>Michael Evans; Thomas Lopez; Daniel Evans; Christopher Johnson; Ravi Yamamoto</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1565,17 +1565,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Indigo Solutions</t>
+          <t>Indigo Labs</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1585,35 +1585,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2012-01-08</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2014-10-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1461.1</v>
+        <v>1446.9</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2509.6</v>
+        <v>4760.9</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>162</v>
+        <v>373.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>254</v>
+        <v>718.5</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>637.2</v>
+        <v>1606.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.909</v>
+        <v>0.293</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>David Ivanov; Michael Lopez; Christopher Williams; Yuki Kim; Wei Ueno</t>
+          <t>Emma Qureshi; Matthew Johnson; Elena Williams; Matthew Qureshi</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Tessera Pharma</t>
+          <t>Stratus Ltd</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1645,35 +1645,35 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2015-08-21</t>
+          <t>2014-01-12</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1856.6</v>
+        <v>401</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2960.6</v>
+        <v>571.2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>358.9</v>
+        <v>57.3</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>788.9</v>
+        <v>99.2</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>402.8</v>
+        <v>153.1</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.891</v>
+        <v>0.493</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Ravi Zhang; Sophie Zhang; Laura Mueller; Yuki Ueno</t>
+          <t>Yuki Rossi; Robert Xu; Amanda Lopez</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -1685,17 +1685,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Beacon Pharma</t>
+          <t>Ember Industries</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1705,35 +1705,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2014-03-07</t>
+          <t>2015-03-26</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2022-04-25</t>
+          <t>2018-06-02</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>445.3</v>
+        <v>1980.1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1290.3</v>
+        <v>2309.3</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>73.40000000000001</v>
+        <v>193.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>154.6</v>
+        <v>188.1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>153.6</v>
+        <v>370.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.55</v>
+        <v>0.548</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Andrew Patel; Emma Xu; Olivia Johnson</t>
+          <t>Yuki Fischer; Amanda Mueller; Hannah Yamamoto; Amanda Ueno</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -1745,107 +1745,115 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Stratus Industries</t>
+          <t>Helix Labs</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2015-06-25</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>2016-10-13</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-21</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
-        <v>1662.8</v>
+        <v>1941.7</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v/>
+        <v>4139.9</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>252.7</v>
+        <v>537.2</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v/>
+        <v>770.7</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>781.5</v>
+        <v>1727.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.656</v>
+        <v>0.945</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Olivia Hassan; Jessica Gupta; Robert Gupta; Yuki Vega; Sophie Brown</t>
+          <t>Wei Ueno; Laura O'Brien; Christopher Ivanov; David Williams; Rachel Anderson</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Glacier Networks</t>
+          <t>Orion Media</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2014-08-04</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>2017-11-26</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>2021-02-22</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n">
-        <v>1952.1</v>
+        <v>1374.3</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v/>
+        <v>1807.1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>357.6</v>
+        <v>231.1</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v/>
+        <v>341.2</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>563.6</v>
+        <v>305.9</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.801</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Ahmed O'Brien; Ahmed Zhang; David Evans; Amanda Schmidt; Ahmed Evans</t>
+          <t>Ravi Patel; Michael Yamamoto; Christopher Patel</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -1857,7 +1865,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Delta SA</t>
+          <t>Helix Inc</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1867,45 +1875,41 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2016-11-25</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2023-12-07</t>
-        </is>
-      </c>
+          <t>2015-12-19</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
-        <v>59.2</v>
+        <v>1363.5</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>159</v>
+        <v/>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.7</v>
+        <v>162.1</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>11.1</v>
+        <v/>
       </c>
       <c r="K27" s="4" t="n">
-        <v>11.3</v>
+        <v>169.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.957</v>
+        <v>0.637</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Yuki Ueno; Thomas Patel; Matthew Gupta</t>
+          <t>Christopher Vega; Daniel Tanaka; Emma Patel</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -1917,17 +1921,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Meridian Health</t>
+          <t>Apex Dynamics</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1937,31 +1941,31 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2016-04-05</t>
+          <t>2015-03-18</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
-        <v>516.9</v>
+        <v>678.5</v>
       </c>
       <c r="H28" s="4" t="n">
         <v/>
       </c>
       <c r="I28" s="4" t="n">
-        <v>124.1</v>
+        <v>132.8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v/>
       </c>
       <c r="K28" s="4" t="n">
-        <v>554.5</v>
+        <v>109.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.825</v>
+        <v>0.32</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Sarah Fischer; Christopher Evans; Laura Nakamura; Priya Gupta</t>
+          <t>Matthew Kim; Wei Tanaka; Elena Xu; Jessica Ivanov</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -1973,17 +1977,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Ember Inc</t>
+          <t>Stratus Networks</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1993,35 +1997,35 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2015-03-20</t>
+          <t>2014-02-24</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2021-04-10</t>
+          <t>2020-12-06</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>726.3</v>
+        <v>1060.1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1822</v>
+        <v>1472.9</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>188.7</v>
+        <v>139.5</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>218.3</v>
+        <v>139.9</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>297.3</v>
+        <v>583.4</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.317</v>
+        <v>0.195</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Laura Qureshi; Sarah O'Brien; Ravi Patel</t>
+          <t>Priya Chen; Sophie Brown; Jennifer Schmidt</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2033,17 +2037,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Lattice Inc</t>
+          <t>Atlas Holdings</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2053,35 +2057,35 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2016-11-19</t>
+          <t>2016-06-15</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2020-01-24</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1445.6</v>
+        <v>1043.6</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1638.3</v>
+        <v>3372.1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>128.1</v>
+        <v>185.4</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>206.1</v>
+        <v>303.7</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>456.3</v>
+        <v>171.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Wei Evans; Sophie Schmidt; Robert Nakamura; Olivia Yamamoto</t>
+          <t>Sarah Evans; David Ivanov; Rachel Davis</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2093,17 +2097,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Krypton Holdings</t>
+          <t>Indigo Industries</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2113,35 +2117,35 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2017-03-24</t>
+          <t>2017-06-13</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1909.6</v>
+        <v>1848.6</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6472.7</v>
+        <v>4363.5</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>406.9</v>
+        <v>239.2</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>611.5</v>
+        <v>207.9</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1757.3</v>
+        <v>170.8</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.463</v>
+        <v>0.452</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Sarah Ueno; Matthew Zhang; Elena Zhang</t>
+          <t>Jennifer Schmidt; Robert Tanaka; Laura Yamamoto; Christopher Xu; Ahmed Schmidt</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2153,17 +2157,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Yields GmbH</t>
+          <t>Fathom Networks</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2173,35 +2177,35 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2016-02-03</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1430.7</v>
+        <v>1269.6</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1108.6</v>
+        <v>3465.4</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>366.6</v>
+        <v>228.3</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>419.6</v>
+        <v>564.6</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>721.4</v>
+        <v>423.7</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.334</v>
+        <v>0.61</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Sarah Hassan; Thomas Ueno; Jessica Evans; Christopher Ueno</t>
+          <t>Ravi Rossi; Wei Mueller; Jennifer Anderson; Mark Johnson</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2213,17 +2217,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Delta Media</t>
+          <t>Meridian AG</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2233,35 +2237,35 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2014-04-14</t>
+          <t>2014-08-16</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2019-03-29</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>806.8</v>
+        <v>986.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2393.1</v>
+        <v>2632.1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>117.1</v>
+        <v>137.2</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>175</v>
+        <v>209.4</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>168.5</v>
+        <v>378.8</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.37</v>
+        <v>0.654</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Sophie Xu; Ahmed Fischer; Christopher Vega; Jessica Tanaka; James Yamamoto</t>
+          <t>Michael Yamamoto; Elena Tanaka</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -2273,7 +2277,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Bloom Health</t>
+          <t>Fathom GmbH</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2283,7 +2287,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2293,35 +2297,35 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2016-07-24</t>
+          <t>2016-10-02</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2019-07-28</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1514.2</v>
+        <v>164.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5295</v>
+        <v>386.9</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>305.5</v>
+        <v>23.9</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>624.3</v>
+        <v>53.4</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>949.7</v>
+        <v>40.8</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.201</v>
+        <v>0.244</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Laura Gupta; Elena Ueno</t>
+          <t>James Zhang; Ravi Fischer; Sophie Brown</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2333,17 +2337,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Quanta AG</t>
+          <t>Xenith Foods</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2353,35 +2357,35 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2018-12-28</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>855.8</v>
+        <v>1420.5</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>923.2</v>
+        <v>1655.9</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>115.6</v>
+        <v>183.3</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>185</v>
+        <v>322.9</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>97</v>
+        <v>660.2</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.173</v>
+        <v>0.393</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Sophie Yamamoto; Rachel Vega; Jennifer Zhang</t>
+          <t>Thomas Vega; Laura Williams; Wei O'Brien</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -2393,17 +2397,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Meridian Media</t>
+          <t>Yields Capital</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2413,35 +2417,35 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1606.5</v>
+        <v>267.9</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>3250.9</v>
+        <v>909.9</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>416.6</v>
+        <v>60.5</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>495.4</v>
+        <v>51</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1505.2</v>
+        <v>148.4</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.427</v>
+        <v>0.669</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Ahmed O'Brien; Emma Davis; Hannah Mueller</t>
+          <t>Laura Fischer; Andrew Chen</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -2453,7 +2457,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Delta Bio</t>
+          <t>Halo Partners</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -2463,7 +2467,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2473,35 +2477,35 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2017-01-08</t>
+          <t>2017-11-16</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1607.4</v>
+        <v>1970.9</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2914.7</v>
+        <v>4860.3</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>431.1</v>
+        <v>470.3</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>517.6</v>
+        <v>422.3</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>444.5</v>
+        <v>1857.3</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.576</v>
+        <v>0.458</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Mark Zhang; Yuki Kim</t>
+          <t>Sarah Brown; Priya Ivanov; Jessica Patel</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2513,17 +2517,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Halo Energy</t>
+          <t>Vertex Media</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2533,31 +2537,31 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
+          <t>2015-11-06</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
-        <v>1634</v>
+        <v>1165</v>
       </c>
       <c r="H38" s="4" t="n">
         <v/>
       </c>
       <c r="I38" s="4" t="n">
-        <v>171.3</v>
+        <v>110.2</v>
       </c>
       <c r="J38" s="4" t="n">
         <v/>
       </c>
       <c r="K38" s="4" t="n">
-        <v>499.7</v>
+        <v>424.9</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.741</v>
+        <v>0.299</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Laura Zhang; Emma Gupta; Robert Yamamoto; Wei Ueno; Christopher Zhang</t>
+          <t>Hannah Brown; Matthew Vega; Mark Zhang; Elena Davis</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
